--- a/xlsx/Power/p9.xlsx
+++ b/xlsx/Power/p9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F82116-C24D-428B-8E87-BD92ECE7B4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D3415-36D5-4572-B240-DAC167721B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{497C96CD-3104-42D4-864B-51CA3242F8AB}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{497C96CD-3104-42D4-864B-51CA3242F8AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,13 +404,13 @@
         <v>0.83699999999999997</v>
       </c>
       <c r="C1">
-        <v>0.97699999999999998</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="D1">
-        <v>0.999</v>
+        <v>0.92100000000000004</v>
       </c>
       <c r="E1">
-        <v>0.999</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="F1">
         <v>1</v>
@@ -436,19 +436,19 @@
         <v>0.79700000000000004</v>
       </c>
       <c r="C2">
-        <v>0.95199999999999996</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="D2">
-        <v>0.995</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="E2">
-        <v>0.997</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -468,10 +468,10 @@
         <v>0.76100000000000001</v>
       </c>
       <c r="C3">
-        <v>0.94099999999999995</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="D3">
-        <v>0.98699999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="E3">
         <v>0.99299999999999999</v>
@@ -494,16 +494,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.37</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="B4">
-        <v>0.70499999999999996</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="C4">
-        <v>0.89800000000000002</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="D4">
-        <v>0.97699999999999998</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="E4">
         <v>0.98699999999999999</v>
@@ -564,16 +564,16 @@
         <v>0.63</v>
       </c>
       <c r="C6">
-        <v>0.82399999999999995</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="D6">
-        <v>0.93300000000000005</v>
+        <v>0.97</v>
       </c>
       <c r="E6">
-        <v>0.97399999999999998</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="F6">
-        <v>0.99</v>
+        <v>0.996</v>
       </c>
       <c r="G6">
         <v>0.998</v>
@@ -596,16 +596,16 @@
         <v>0.59</v>
       </c>
       <c r="C7">
-        <v>0.76800000000000002</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="D7">
         <v>0.89</v>
       </c>
       <c r="E7">
-        <v>0.95499999999999996</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="F7">
-        <v>0.98899999999999999</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="G7">
         <v>0.996</v>
@@ -628,16 +628,16 @@
         <v>0.80900000000000005</v>
       </c>
       <c r="C8">
-        <v>0.96199999999999997</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="D8">
-        <v>0.98499999999999999</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="E8">
-        <v>0.998</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.995</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.41899999999999998</v>
       </c>
       <c r="C9">
-        <v>0.248</v>
+        <v>0.70299999999999996</v>
       </c>
       <c r="D9">
-        <v>0.20399999999999999</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="E9">
-        <v>0.22600000000000001</v>
+        <v>0.84599999999999997</v>
       </c>
       <c r="F9">
-        <v>0.26400000000000001</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="G9">
-        <v>0.32600000000000001</v>
+        <v>0.439</v>
       </c>
       <c r="H9">
-        <v>0.38700000000000001</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="I9">
-        <v>0.45100000000000001</v>
+        <v>0.498</v>
       </c>
       <c r="J9">
-        <v>0.53200000000000003</v>
+        <v>0.55500000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p9.xlsx
+++ b/xlsx/Power/p9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D3415-36D5-4572-B240-DAC167721B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2762D13-A773-45C9-9405-AA922ED2DC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{497C96CD-3104-42D4-864B-51CA3242F8AB}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{497C96CD-3104-42D4-864B-51CA3242F8AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.43</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="B1">
         <v>0.83699999999999997</v>
       </c>
       <c r="C1">
-        <v>0.54900000000000004</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="D1">
-        <v>0.92100000000000004</v>
+        <v>0.999</v>
       </c>
       <c r="E1">
-        <v>0.98899999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="F1">
         <v>1</v>
@@ -436,19 +436,19 @@
         <v>0.79700000000000004</v>
       </c>
       <c r="C2">
-        <v>0.53600000000000003</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="D2">
-        <v>0.88900000000000001</v>
+        <v>0.995</v>
       </c>
       <c r="E2">
-        <v>0.98399999999999999</v>
+        <v>0.997</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -468,10 +468,10 @@
         <v>0.76100000000000001</v>
       </c>
       <c r="C3">
-        <v>0.95699999999999996</v>
+        <v>0.94099999999999995</v>
       </c>
       <c r="D3">
-        <v>0.99</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="E3">
         <v>0.99299999999999999</v>
@@ -494,16 +494,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.40200000000000002</v>
+        <v>0.37</v>
       </c>
       <c r="B4">
-        <v>0.71599999999999997</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="C4">
-        <v>0.90200000000000002</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="D4">
-        <v>0.97499999999999998</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="E4">
         <v>0.98699999999999999</v>
@@ -558,22 +558,22 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.34499999999999997</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="B6">
         <v>0.63</v>
       </c>
       <c r="C6">
-        <v>0.95799999999999996</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="D6">
-        <v>0.97</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="E6">
-        <v>0.98399999999999999</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="F6">
-        <v>0.996</v>
+        <v>0.99</v>
       </c>
       <c r="G6">
         <v>0.998</v>
@@ -596,16 +596,16 @@
         <v>0.59</v>
       </c>
       <c r="C7">
-        <v>0.75900000000000001</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="D7">
         <v>0.89</v>
       </c>
       <c r="E7">
-        <v>0.95599999999999996</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="F7">
-        <v>0.98799999999999999</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="G7">
         <v>0.996</v>
@@ -628,16 +628,16 @@
         <v>0.80900000000000005</v>
       </c>
       <c r="C8">
-        <v>5.0999999999999997E-2</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="D8">
-        <v>0.83799999999999997</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="E8">
-        <v>0.97199999999999998</v>
+        <v>0.998</v>
       </c>
       <c r="F8">
-        <v>0.995</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.41899999999999998</v>
       </c>
       <c r="C9">
-        <v>0.70299999999999996</v>
+        <v>0.248</v>
       </c>
       <c r="D9">
-        <v>0.98499999999999999</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="E9">
-        <v>0.84599999999999997</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="F9">
-        <v>0.48599999999999999</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G9">
-        <v>0.439</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="H9">
-        <v>0.45300000000000001</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="I9">
-        <v>0.498</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="J9">
-        <v>0.55500000000000005</v>
+        <v>0.53200000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p9.xlsx
+++ b/xlsx/Power/p9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2762D13-A773-45C9-9405-AA922ED2DC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6062578C-63AF-44A4-BFD0-25835DF34826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{497C96CD-3104-42D4-864B-51CA3242F8AB}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{497C96CD-3104-42D4-864B-51CA3242F8AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,7 +398,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.43099999999999999</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="B1">
         <v>0.83699999999999997</v>
@@ -430,13 +430,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.40799999999999997</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="B2">
         <v>0.79700000000000004</v>
       </c>
       <c r="C2">
-        <v>0.95199999999999996</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="D2">
         <v>0.995</v>
@@ -462,16 +462,16 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.39</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="B3">
-        <v>0.76100000000000001</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="C3">
-        <v>0.94099999999999995</v>
+        <v>0.94299999999999995</v>
       </c>
       <c r="D3">
-        <v>0.98699999999999999</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="E3">
         <v>0.99299999999999999</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.37</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="B4">
-        <v>0.70499999999999996</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="C4">
-        <v>0.89800000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="D4">
         <v>0.97699999999999998</v>
@@ -526,51 +526,51 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.255</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.871</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.91400000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.34599999999999997</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="B6">
-        <v>0.63</v>
+        <v>0.629</v>
       </c>
       <c r="C6">
-        <v>0.82399999999999995</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="D6">
-        <v>0.93300000000000005</v>
+        <v>0.93</v>
       </c>
       <c r="E6">
-        <v>0.97399999999999998</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="F6">
         <v>0.99</v>
@@ -590,16 +590,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.32900000000000001</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="B7">
-        <v>0.59</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="C7">
-        <v>0.76800000000000002</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="D7">
-        <v>0.89</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="E7">
         <v>0.95499999999999996</v>
@@ -631,7 +631,7 @@
         <v>0.96199999999999997</v>
       </c>
       <c r="D8">
-        <v>0.98499999999999999</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="E8">
         <v>0.998</v>
@@ -654,34 +654,34 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.23200000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="B9">
-        <v>0.41899999999999998</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="C9">
-        <v>0.248</v>
+        <v>0.249</v>
       </c>
       <c r="D9">
-        <v>0.20399999999999999</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="E9">
-        <v>0.22600000000000001</v>
+        <v>0.223</v>
       </c>
       <c r="F9">
-        <v>0.26400000000000001</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="G9">
-        <v>0.32600000000000001</v>
+        <v>0.32200000000000001</v>
       </c>
       <c r="H9">
-        <v>0.38700000000000001</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="I9">
-        <v>0.45100000000000001</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="J9">
-        <v>0.53200000000000003</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
